--- a/docs/data_dictionary_v1.xlsx
+++ b/docs/data_dictionary_v1.xlsx
@@ -164,16 +164,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FieldsTable" displayName="FieldsTable" ref="A5:G343" headerRowCount="1">
-  <autoFilter ref="A5:G343"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FieldsTable" displayName="FieldsTable" ref="A5:H344" headerRowCount="1">
+  <autoFilter ref="A5:H344"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="Object"/>
     <tableColumn id="2" name="Column"/>
     <tableColumn id="3" name="Type"/>
     <tableColumn id="4" name="PK/FK/uniqueness"/>
     <tableColumn id="5" name="Nullable"/>
     <tableColumn id="6" name="Meaning"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="7" name="Owner"/>
+    <tableColumn id="8" name="Default"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -185,7 +186,7 @@
   <tableColumns count="4">
     <tableColumn id="1" name="Object"/>
     <tableColumn id="2" name="One row represents"/>
-    <tableColumn id="3" name="Definition status"/>
+    <tableColumn id="3" name="Owner"/>
     <tableColumn id="4" name="Columns"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>

--- a/docs/data_dictionary_v1.xlsx
+++ b/docs/data_dictionary_v1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\SN3PEPF000190DE\EXCELCNV\d28bf187-ed25-40df-a6b6-405c2d09bd49\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\SY3PEPF00001B31\EXCELCNV\6c3721b5-d814-4458-bc34-45ea50e7f773\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{267B28D7-499D-4F32-A923-003B6B875FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78C0237A-BA77-42AC-963B-9A65F0D31E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2905" uniqueCount="463">
   <si>
     <t>GlucoLink data dictionary</t>
   </si>
@@ -53,13 +53,13 @@
     <t/>
   </si>
   <si>
-    <t>Database: glucolink_a2. 47 objects / 339 columns.</t>
-  </si>
-  <si>
-    <t>Sources: catalog 3f7e03e (8 Oct); 04 d4ed184 and 07 833d05d (9 Oct). New SQL definitions have not been rerun by B.</t>
-  </si>
-  <si>
-    <t>Planned objects: reporting.vw_uc1_care_gaps, reporting.vw_uc2_pdc, reporting.vw_uc3_hba1c_trend, reporting.vw_uc4_care_path_breaks, audit.test_result. Planned PK / Planned FK are design constraints only; views have no PK.</t>
+    <t>Database: glucolink_a2. 47 objects / 338 columns.</t>
+  </si>
+  <si>
+    <t>Source: main 9a499ce4c1564dfdc06e5a521d714d6728337332; glucolink_a2_test rebuilt and rerun on 11 October 2026. Both 00–09 runs passed 46/46 tests.</t>
+  </si>
+  <si>
+    <t>All 47 objects are implemented. Catalog verified: 338 columns and 24 enforced FKs. Views have no PK/FK constraints.</t>
   </si>
   <si>
     <t>Object</t>
@@ -497,9 +497,6 @@
     <t>bigint</t>
   </si>
   <si>
-    <t>Logical reference audit.pipeline_run.run_id (not enforced)</t>
-  </si>
-  <si>
     <t>Ingestion run reference for traceability; not a RAW FK</t>
   </si>
   <si>
@@ -542,9 +539,6 @@
     <t>cleansed.dispense</t>
   </si>
   <si>
-    <t>PRIMARY KEY</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -554,6 +548,9 @@
     <t>issue_id</t>
   </si>
   <si>
+    <t>PRIMARY KEY (issue_id)</t>
+  </si>
+  <si>
     <t>Automatically generated data-quality issue identifier</t>
   </si>
   <si>
@@ -647,9 +644,6 @@
     <t>returned_at</t>
   </si>
   <si>
-    <t>timestamptz</t>
-  </si>
-  <si>
     <t>Result-return timestamp, if any</t>
   </si>
   <si>
@@ -704,7 +698,7 @@
     <t>cleansed.patient_source_link</t>
   </si>
   <si>
-    <t>Logical reference to cleansed.patient_master(patient_id); not enforced in current 05</t>
+    <t>FOREIGN KEY (patient_id) REFERENCES cleansed.patient_master(patient_id)</t>
   </si>
   <si>
     <t>match_status</t>
@@ -905,22 +899,25 @@
     <t>dispense_key</t>
   </si>
   <si>
+    <t>PRIMARY KEY (dispense_key)</t>
+  </si>
+  <si>
     <t>Surrogate dispensing fact key</t>
   </si>
   <si>
-    <t>UNIQUE</t>
-  </si>
-  <si>
-    <t>FOREIGN KEY → curated.dim_patient(patient_key)</t>
-  </si>
-  <si>
-    <t>FOREIGN KEY → curated.dim_date(date_key)</t>
-  </si>
-  <si>
-    <t>FOREIGN KEY → curated.dim_pharmacy(pharmacy_key)</t>
-  </si>
-  <si>
-    <t>FOREIGN KEY → curated.dim_medication(medication_key)</t>
+    <t>UNIQUE (dispense_id)</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (patient_key) REFERENCES curated.dim_patient(patient_key)</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (date_key) REFERENCES curated.dim_date(date_key)</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (pharmacy_key) REFERENCES curated.dim_pharmacy(pharmacy_key)</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (medication_key) REFERENCES curated.dim_medication(medication_key)</t>
   </si>
   <si>
     <t>curated.fact_encounter</t>
@@ -929,10 +926,16 @@
     <t>encounter_key</t>
   </si>
   <si>
+    <t>PRIMARY KEY (encounter_key)</t>
+  </si>
+  <si>
     <t>Surrogate encounter fact key</t>
   </si>
   <si>
-    <t>FOREIGN KEY → curated.dim_clinic(clinic_key)</t>
+    <t>UNIQUE (encounter_id)</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (clinic_key) REFERENCES curated.dim_clinic(clinic_key)</t>
   </si>
   <si>
     <t>curated.fact_lab_result</t>
@@ -941,25 +944,37 @@
     <t>lab_result_key</t>
   </si>
   <si>
+    <t>PRIMARY KEY (lab_result_key)</t>
+  </si>
+  <si>
     <t>Surrogate laboratory fact key</t>
   </si>
   <si>
+    <t>UNIQUE (message_id)</t>
+  </si>
+  <si>
     <t>collected_date_key</t>
   </si>
   <si>
+    <t>FOREIGN KEY (collected_date_key) REFERENCES curated.dim_date(date_key)</t>
+  </si>
+  <si>
     <t>Role-playing date key for collection</t>
   </si>
   <si>
     <t>reported_date_key</t>
   </si>
   <si>
+    <t>FOREIGN KEY (reported_date_key) REFERENCES curated.dim_date(date_key)</t>
+  </si>
+  <si>
     <t>Role-playing date key for reporting</t>
   </si>
   <si>
-    <t>FOREIGN KEY → curated.dim_lab(lab_key)</t>
-  </si>
-  <si>
-    <t>FOREIGN KEY → curated.dim_test(test_key)</t>
+    <t>FOREIGN KEY (lab_key) REFERENCES curated.dim_lab(lab_key)</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY (test_key) REFERENCES curated.dim_test(test_key)</t>
   </si>
   <si>
     <t>Standardised HbA1c rounded to one decimal</t>
@@ -1001,9 +1016,6 @@
     <t>reporting.vw_uc1_care_gaps</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>home_clinic</t>
   </si>
   <si>
@@ -1235,6 +1247,9 @@
     <t>test_id</t>
   </si>
   <si>
+    <t>PRIMARY KEY (test_id)</t>
+  </si>
+  <si>
     <t>Acceptance-test identifier</t>
   </si>
   <si>
@@ -1257,6 +1272,9 @@
   </si>
   <si>
     <t>Whether the acceptance comparison passed</t>
+  </si>
+  <si>
+    <t>GENERATED ALWAYS AS ((NOT (actual IS DISTINCT FROM expected))) STORED</t>
   </si>
   <si>
     <t>GlucoLink object catalogue</t>
@@ -1800,7 +1818,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H344"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3669,13 +3687,13 @@
         <v>149</v>
       </c>
       <c r="D72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>19</v>
@@ -3689,7 +3707,7 @@
         <v>143</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>87</v>
@@ -3701,7 +3719,7 @@
         <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>19</v>
@@ -3712,7 +3730,7 @@
     </row>
     <row r="74" spans="1:8" ht="42" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>30</v>
@@ -3738,7 +3756,7 @@
     </row>
     <row r="75" spans="1:8" ht="42" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>33</v>
@@ -3764,7 +3782,7 @@
     </row>
     <row r="76" spans="1:8" ht="42" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>14</v>
@@ -3790,7 +3808,7 @@
     </row>
     <row r="77" spans="1:8" ht="42" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>37</v>
@@ -3816,7 +3834,7 @@
     </row>
     <row r="78" spans="1:8" ht="42" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>40</v>
@@ -3842,7 +3860,7 @@
     </row>
     <row r="79" spans="1:8" ht="42" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>42</v>
@@ -3868,7 +3886,7 @@
     </row>
     <row r="80" spans="1:8" ht="42" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>44</v>
@@ -3894,7 +3912,7 @@
     </row>
     <row r="81" spans="1:8" ht="42" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>47</v>
@@ -3920,7 +3938,7 @@
     </row>
     <row r="82" spans="1:8" ht="42" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>144</v>
@@ -3946,7 +3964,7 @@
     </row>
     <row r="83" spans="1:8" ht="42" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>146</v>
@@ -3972,7 +3990,7 @@
     </row>
     <row r="84" spans="1:8" ht="42" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>148</v>
@@ -3981,13 +3999,13 @@
         <v>149</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>19</v>
@@ -3998,10 +4016,10 @@
     </row>
     <row r="85" spans="1:8" ht="42" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>87</v>
@@ -4013,7 +4031,7 @@
         <v>23</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>19</v>
@@ -4024,7 +4042,7 @@
     </row>
     <row r="86" spans="1:8" ht="42" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>33</v>
@@ -4050,7 +4068,7 @@
     </row>
     <row r="87" spans="1:8" ht="42" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>51</v>
@@ -4076,7 +4094,7 @@
     </row>
     <row r="88" spans="1:8" ht="42" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>53</v>
@@ -4102,7 +4120,7 @@
     </row>
     <row r="89" spans="1:8" ht="42" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>55</v>
@@ -4128,7 +4146,7 @@
     </row>
     <row r="90" spans="1:8" ht="42" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>57</v>
@@ -4154,7 +4172,7 @@
     </row>
     <row r="91" spans="1:8" ht="42" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>27</v>
@@ -4180,7 +4198,7 @@
     </row>
     <row r="92" spans="1:8" ht="42" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>60</v>
@@ -4206,7 +4224,7 @@
     </row>
     <row r="93" spans="1:8" ht="42" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>14</v>
@@ -4232,7 +4250,7 @@
     </row>
     <row r="94" spans="1:8" ht="42" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
@@ -4258,7 +4276,7 @@
     </row>
     <row r="95" spans="1:8" ht="42" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>144</v>
@@ -4284,7 +4302,7 @@
     </row>
     <row r="96" spans="1:8" ht="42" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>146</v>
@@ -4310,7 +4328,7 @@
     </row>
     <row r="97" spans="1:8" ht="42" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>148</v>
@@ -4319,13 +4337,13 @@
         <v>149</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>19</v>
@@ -4336,10 +4354,10 @@
     </row>
     <row r="98" spans="1:8" ht="42" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>87</v>
@@ -4351,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>19</v>
@@ -4362,7 +4380,7 @@
     </row>
     <row r="99" spans="1:8" ht="42" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>93</v>
@@ -4388,7 +4406,7 @@
     </row>
     <row r="100" spans="1:8" ht="42" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>80</v>
@@ -4414,7 +4432,7 @@
     </row>
     <row r="101" spans="1:8" ht="42" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>14</v>
@@ -4440,7 +4458,7 @@
     </row>
     <row r="102" spans="1:8" ht="42" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>97</v>
@@ -4466,7 +4484,7 @@
     </row>
     <row r="103" spans="1:8" ht="42" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>144</v>
@@ -4492,7 +4510,7 @@
     </row>
     <row r="104" spans="1:8" ht="42" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>146</v>
@@ -4518,7 +4536,7 @@
     </row>
     <row r="105" spans="1:8" ht="42" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>148</v>
@@ -4527,13 +4545,13 @@
         <v>149</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>19</v>
@@ -4544,10 +4562,10 @@
     </row>
     <row r="106" spans="1:8" ht="42" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>87</v>
@@ -4559,7 +4577,7 @@
         <v>23</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>19</v>
@@ -4570,7 +4588,7 @@
     </row>
     <row r="107" spans="1:8" ht="42" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>72</v>
@@ -4596,7 +4614,7 @@
     </row>
     <row r="108" spans="1:8" ht="42" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>75</v>
@@ -4622,7 +4640,7 @@
     </row>
     <row r="109" spans="1:8" ht="42" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>77</v>
@@ -4648,7 +4666,7 @@
     </row>
     <row r="110" spans="1:8" ht="42" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>144</v>
@@ -4674,7 +4692,7 @@
     </row>
     <row r="111" spans="1:8" ht="42" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>146</v>
@@ -4700,7 +4718,7 @@
     </row>
     <row r="112" spans="1:8" ht="42" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>148</v>
@@ -4709,13 +4727,13 @@
         <v>149</v>
       </c>
       <c r="D112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>19</v>
@@ -4726,10 +4744,10 @@
     </row>
     <row r="113" spans="1:8" ht="42" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>87</v>
@@ -4741,7 +4759,7 @@
         <v>23</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>19</v>
@@ -4752,7 +4770,7 @@
     </row>
     <row r="114" spans="1:8" ht="42" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>80</v>
@@ -4778,7 +4796,7 @@
     </row>
     <row r="115" spans="1:8" ht="42" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>72</v>
@@ -4804,7 +4822,7 @@
     </row>
     <row r="116" spans="1:8" ht="42" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>65</v>
@@ -4830,7 +4848,7 @@
     </row>
     <row r="117" spans="1:8" ht="42" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>86</v>
@@ -4856,7 +4874,7 @@
     </row>
     <row r="118" spans="1:8" ht="42" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>89</v>
@@ -4882,7 +4900,7 @@
     </row>
     <row r="119" spans="1:8" ht="42" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>144</v>
@@ -4908,7 +4926,7 @@
     </row>
     <row r="120" spans="1:8" ht="42" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>146</v>
@@ -4934,7 +4952,7 @@
     </row>
     <row r="121" spans="1:8" ht="42" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>148</v>
@@ -4943,13 +4961,13 @@
         <v>149</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>19</v>
@@ -4960,10 +4978,10 @@
     </row>
     <row r="122" spans="1:8" ht="42" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>87</v>
@@ -4975,7 +4993,7 @@
         <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>19</v>
@@ -4986,7 +5004,7 @@
     </row>
     <row r="123" spans="1:8" ht="42" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>65</v>
@@ -5012,7 +5030,7 @@
     </row>
     <row r="124" spans="1:8" ht="42" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>68</v>
@@ -5038,7 +5056,7 @@
     </row>
     <row r="125" spans="1:8" ht="42" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>55</v>
@@ -5064,7 +5082,7 @@
     </row>
     <row r="126" spans="1:8" ht="42" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>57</v>
@@ -5090,7 +5108,7 @@
     </row>
     <row r="127" spans="1:8" ht="42" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>60</v>
@@ -5116,7 +5134,7 @@
     </row>
     <row r="128" spans="1:8" ht="42" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>144</v>
@@ -5142,7 +5160,7 @@
     </row>
     <row r="129" spans="1:8" ht="42" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>146</v>
@@ -5168,7 +5186,7 @@
     </row>
     <row r="130" spans="1:8" ht="42" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>148</v>
@@ -5177,13 +5195,13 @@
         <v>149</v>
       </c>
       <c r="D130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>19</v>
@@ -5194,10 +5212,10 @@
     </row>
     <row r="131" spans="1:8" ht="42" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>87</v>
@@ -5209,7 +5227,7 @@
         <v>23</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>19</v>
@@ -5220,7 +5238,7 @@
     </row>
     <row r="132" spans="1:8" ht="42" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>100</v>
@@ -5246,7 +5264,7 @@
     </row>
     <row r="133" spans="1:8" ht="42" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>103</v>
@@ -5272,7 +5290,7 @@
     </row>
     <row r="134" spans="1:8" ht="42" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>106</v>
@@ -5298,7 +5316,7 @@
     </row>
     <row r="135" spans="1:8" ht="42" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>109</v>
@@ -5324,7 +5342,7 @@
     </row>
     <row r="136" spans="1:8" ht="42" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>112</v>
@@ -5350,7 +5368,7 @@
     </row>
     <row r="137" spans="1:8" ht="42" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>114</v>
@@ -5376,7 +5394,7 @@
     </row>
     <row r="138" spans="1:8" ht="42" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>116</v>
@@ -5402,7 +5420,7 @@
     </row>
     <row r="139" spans="1:8" ht="42" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>144</v>
@@ -5428,7 +5446,7 @@
     </row>
     <row r="140" spans="1:8" ht="42" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>146</v>
@@ -5454,7 +5472,7 @@
     </row>
     <row r="141" spans="1:8" ht="42" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>148</v>
@@ -5463,13 +5481,13 @@
         <v>149</v>
       </c>
       <c r="D141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>19</v>
@@ -5480,10 +5498,10 @@
     </row>
     <row r="142" spans="1:8" ht="42" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>87</v>
@@ -5495,7 +5513,7 @@
         <v>23</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>19</v>
@@ -5506,7 +5524,7 @@
     </row>
     <row r="143" spans="1:8" ht="42" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>109</v>
@@ -5532,7 +5550,7 @@
     </row>
     <row r="144" spans="1:8" ht="42" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>120</v>
@@ -5558,7 +5576,7 @@
     </row>
     <row r="145" spans="1:8" ht="42" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>122</v>
@@ -5584,7 +5602,7 @@
     </row>
     <row r="146" spans="1:8" ht="42" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>124</v>
@@ -5610,7 +5628,7 @@
     </row>
     <row r="147" spans="1:8" ht="42" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>126</v>
@@ -5636,7 +5654,7 @@
     </row>
     <row r="148" spans="1:8" ht="42" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>129</v>
@@ -5662,7 +5680,7 @@
     </row>
     <row r="149" spans="1:8" ht="42" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>144</v>
@@ -5688,7 +5706,7 @@
     </row>
     <row r="150" spans="1:8" ht="42" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>146</v>
@@ -5714,7 +5732,7 @@
     </row>
     <row r="151" spans="1:8" ht="42" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>148</v>
@@ -5723,13 +5741,13 @@
         <v>149</v>
       </c>
       <c r="D151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>19</v>
@@ -5740,10 +5758,10 @@
     </row>
     <row r="152" spans="1:8" ht="42" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>87</v>
@@ -5755,7 +5773,7 @@
         <v>23</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>19</v>
@@ -5766,7 +5784,7 @@
     </row>
     <row r="153" spans="1:8" ht="42" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>103</v>
@@ -5792,7 +5810,7 @@
     </row>
     <row r="154" spans="1:8" ht="42" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>137</v>
@@ -5818,7 +5836,7 @@
     </row>
     <row r="155" spans="1:8" ht="42" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>139</v>
@@ -5844,7 +5862,7 @@
     </row>
     <row r="156" spans="1:8" ht="42" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>141</v>
@@ -5870,7 +5888,7 @@
     </row>
     <row r="157" spans="1:8" ht="42" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>60</v>
@@ -5896,7 +5914,7 @@
     </row>
     <row r="158" spans="1:8" ht="42" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>106</v>
@@ -5922,7 +5940,7 @@
     </row>
     <row r="159" spans="1:8" ht="42" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>144</v>
@@ -5948,7 +5966,7 @@
     </row>
     <row r="160" spans="1:8" ht="42" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>146</v>
@@ -5974,7 +5992,7 @@
     </row>
     <row r="161" spans="1:8" ht="42" customHeight="1">
       <c r="A161" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>148</v>
@@ -5983,13 +6001,13 @@
         <v>149</v>
       </c>
       <c r="D161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>19</v>
@@ -6000,10 +6018,10 @@
     </row>
     <row r="162" spans="1:8" ht="42" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>87</v>
@@ -6015,7 +6033,7 @@
         <v>23</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>19</v>
@@ -6026,7 +6044,7 @@
     </row>
     <row r="163" spans="1:8" ht="42" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>106</v>
@@ -6052,7 +6070,7 @@
     </row>
     <row r="164" spans="1:8" ht="42" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>133</v>
@@ -6078,7 +6096,7 @@
     </row>
     <row r="165" spans="1:8" ht="42" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>25</v>
@@ -6104,7 +6122,7 @@
     </row>
     <row r="166" spans="1:8" ht="42" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>144</v>
@@ -6130,7 +6148,7 @@
     </row>
     <row r="167" spans="1:8" ht="42" customHeight="1">
       <c r="A167" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>146</v>
@@ -6156,7 +6174,7 @@
     </row>
     <row r="168" spans="1:8" ht="42" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>148</v>
@@ -6165,13 +6183,13 @@
         <v>149</v>
       </c>
       <c r="D168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>19</v>
@@ -6182,10 +6200,10 @@
     </row>
     <row r="169" spans="1:8" ht="42" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>87</v>
@@ -6197,7 +6215,7 @@
         <v>23</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>19</v>
@@ -6208,7 +6226,7 @@
     </row>
     <row r="170" spans="1:8" ht="42" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>100</v>
@@ -6217,7 +6235,7 @@
         <v>22</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>17</v>
@@ -6226,7 +6244,7 @@
         <v>102</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>20</v>
@@ -6234,7 +6252,7 @@
     </row>
     <row r="171" spans="1:8" ht="42" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>103</v>
@@ -6252,7 +6270,7 @@
         <v>105</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>20</v>
@@ -6260,7 +6278,7 @@
     </row>
     <row r="172" spans="1:8" ht="42" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>106</v>
@@ -6278,7 +6296,7 @@
         <v>108</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>20</v>
@@ -6286,7 +6304,7 @@
     </row>
     <row r="173" spans="1:8" ht="42" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>109</v>
@@ -6304,7 +6322,7 @@
         <v>111</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>20</v>
@@ -6312,7 +6330,7 @@
     </row>
     <row r="174" spans="1:8" ht="42" customHeight="1">
       <c r="A174" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>112</v>
@@ -6330,7 +6348,7 @@
         <v>113</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>20</v>
@@ -6338,7 +6356,7 @@
     </row>
     <row r="175" spans="1:8" ht="42" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>114</v>
@@ -6356,7 +6374,7 @@
         <v>115</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>20</v>
@@ -6364,7 +6382,7 @@
     </row>
     <row r="176" spans="1:8" ht="42" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>116</v>
@@ -6382,7 +6400,7 @@
         <v>117</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>20</v>
@@ -6390,36 +6408,36 @@
     </row>
     <row r="177" spans="1:8" ht="42" customHeight="1">
       <c r="A177" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H177" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H177" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="42" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>22</v>
@@ -6431,10 +6449,10 @@
         <v>17</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>20</v>
@@ -6442,10 +6460,10 @@
     </row>
     <row r="179" spans="1:8" ht="42" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>22</v>
@@ -6457,10 +6475,10 @@
         <v>17</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>20</v>
@@ -6468,10 +6486,10 @@
     </row>
     <row r="180" spans="1:8" ht="42" customHeight="1">
       <c r="A180" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>22</v>
@@ -6483,10 +6501,10 @@
         <v>17</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>20</v>
@@ -6494,25 +6512,25 @@
     </row>
     <row r="181" spans="1:8" ht="42" customHeight="1">
       <c r="A181" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="G181" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>20</v>
@@ -6520,7 +6538,7 @@
     </row>
     <row r="182" spans="1:8" ht="42" customHeight="1">
       <c r="A182" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>30</v>
@@ -6529,7 +6547,7 @@
         <v>22</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>17</v>
@@ -6538,7 +6556,7 @@
         <v>32</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>20</v>
@@ -6546,7 +6564,7 @@
     </row>
     <row r="183" spans="1:8" ht="42" customHeight="1">
       <c r="A183" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>33</v>
@@ -6564,7 +6582,7 @@
         <v>35</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>20</v>
@@ -6572,7 +6590,7 @@
     </row>
     <row r="184" spans="1:8" ht="42" customHeight="1">
       <c r="A184" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>14</v>
@@ -6590,7 +6608,7 @@
         <v>18</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>20</v>
@@ -6598,7 +6616,7 @@
     </row>
     <row r="185" spans="1:8" ht="42" customHeight="1">
       <c r="A185" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>37</v>
@@ -6616,7 +6634,7 @@
         <v>39</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>20</v>
@@ -6624,7 +6642,7 @@
     </row>
     <row r="186" spans="1:8" ht="42" customHeight="1">
       <c r="A186" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>40</v>
@@ -6642,7 +6660,7 @@
         <v>41</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>20</v>
@@ -6650,7 +6668,7 @@
     </row>
     <row r="187" spans="1:8" ht="42" customHeight="1">
       <c r="A187" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>42</v>
@@ -6668,7 +6686,7 @@
         <v>43</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>20</v>
@@ -6676,7 +6694,7 @@
     </row>
     <row r="188" spans="1:8" ht="42" customHeight="1">
       <c r="A188" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>44</v>
@@ -6694,7 +6712,7 @@
         <v>46</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H188" s="1" t="s">
         <v>20</v>
@@ -6702,7 +6720,7 @@
     </row>
     <row r="189" spans="1:8" ht="42" customHeight="1">
       <c r="A189" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>47</v>
@@ -6720,7 +6738,7 @@
         <v>48</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>20</v>
@@ -6728,7 +6746,7 @@
     </row>
     <row r="190" spans="1:8" ht="42" customHeight="1">
       <c r="A190" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>80</v>
@@ -6737,7 +6755,7 @@
         <v>22</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>17</v>
@@ -6746,7 +6764,7 @@
         <v>82</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>20</v>
@@ -6754,7 +6772,7 @@
     </row>
     <row r="191" spans="1:8" ht="42" customHeight="1">
       <c r="A191" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>72</v>
@@ -6772,7 +6790,7 @@
         <v>74</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>20</v>
@@ -6780,7 +6798,7 @@
     </row>
     <row r="192" spans="1:8" ht="42" customHeight="1">
       <c r="A192" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>65</v>
@@ -6798,7 +6816,7 @@
         <v>67</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>20</v>
@@ -6806,25 +6824,25 @@
     </row>
     <row r="193" spans="1:8" ht="42" customHeight="1">
       <c r="A193" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="C193" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F193" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="G193" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>20</v>
@@ -6832,25 +6850,25 @@
     </row>
     <row r="194" spans="1:8" ht="42" customHeight="1">
       <c r="A194" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F194" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="G194" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>20</v>
@@ -6858,25 +6876,25 @@
     </row>
     <row r="195" spans="1:8" ht="42" customHeight="1">
       <c r="A195" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B195" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F195" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="G195" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>20</v>
@@ -6884,25 +6902,25 @@
     </row>
     <row r="196" spans="1:8" ht="42" customHeight="1">
       <c r="A196" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F196" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="G196" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>20</v>
@@ -6910,25 +6928,25 @@
     </row>
     <row r="197" spans="1:8" ht="42" customHeight="1">
       <c r="A197" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B197" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F197" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="G197" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>20</v>
@@ -6936,25 +6954,25 @@
     </row>
     <row r="198" spans="1:8" ht="42" customHeight="1">
       <c r="A198" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B198" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="G198" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>20</v>
@@ -6962,10 +6980,10 @@
     </row>
     <row r="199" spans="1:8" ht="42" customHeight="1">
       <c r="A199" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>38</v>
@@ -6977,10 +6995,10 @@
         <v>23</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H199" s="1" t="s">
         <v>20</v>
@@ -6988,10 +7006,10 @@
     </row>
     <row r="200" spans="1:8" ht="42" customHeight="1">
       <c r="A200" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>38</v>
@@ -7003,10 +7021,10 @@
         <v>23</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>20</v>
@@ -7014,10 +7032,10 @@
     </row>
     <row r="201" spans="1:8" ht="42" customHeight="1">
       <c r="A201" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>15</v>
@@ -7029,10 +7047,10 @@
         <v>23</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>20</v>
@@ -7040,25 +7058,25 @@
     </row>
     <row r="202" spans="1:8" ht="42" customHeight="1">
       <c r="A202" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F202" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="G202" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H202" s="1" t="s">
         <v>20</v>
@@ -7066,10 +7084,10 @@
     </row>
     <row r="203" spans="1:8" ht="42" customHeight="1">
       <c r="A203" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>22</v>
@@ -7081,10 +7099,10 @@
         <v>17</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>20</v>
@@ -7092,25 +7110,25 @@
     </row>
     <row r="204" spans="1:8" ht="42" customHeight="1">
       <c r="A204" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>20</v>
@@ -7118,7 +7136,7 @@
     </row>
     <row r="205" spans="1:8" ht="42" customHeight="1">
       <c r="A205" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>137</v>
@@ -7136,7 +7154,7 @@
         <v>138</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>20</v>
@@ -7144,10 +7162,10 @@
     </row>
     <row r="206" spans="1:8" ht="42" customHeight="1">
       <c r="A206" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>22</v>
@@ -7159,10 +7177,10 @@
         <v>23</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>20</v>
@@ -7170,7 +7188,7 @@
     </row>
     <row r="207" spans="1:8" ht="42" customHeight="1">
       <c r="A207" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>55</v>
@@ -7188,7 +7206,7 @@
         <v>56</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H207" s="1" t="s">
         <v>20</v>
@@ -7196,7 +7214,7 @@
     </row>
     <row r="208" spans="1:8" ht="42" customHeight="1">
       <c r="A208" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>57</v>
@@ -7214,7 +7232,7 @@
         <v>59</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>20</v>
@@ -7222,10 +7240,10 @@
     </row>
     <row r="209" spans="1:8" ht="42" customHeight="1">
       <c r="A209" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>22</v>
@@ -7237,10 +7255,10 @@
         <v>23</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>20</v>
@@ -7248,25 +7266,25 @@
     </row>
     <row r="210" spans="1:8" ht="42" customHeight="1">
       <c r="A210" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>20</v>
@@ -7274,16 +7292,16 @@
     </row>
     <row r="211" spans="1:8" ht="42" customHeight="1">
       <c r="A211" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>17</v>
@@ -7292,7 +7310,7 @@
         <v>215</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>20</v>
@@ -7300,25 +7318,25 @@
     </row>
     <row r="212" spans="1:8" ht="42" customHeight="1">
       <c r="A212" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H212" s="1" t="s">
         <v>20</v>
@@ -7326,10 +7344,10 @@
     </row>
     <row r="213" spans="1:8" ht="42" customHeight="1">
       <c r="A213" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>22</v>
@@ -7341,10 +7359,10 @@
         <v>23</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>20</v>
@@ -7352,13 +7370,13 @@
     </row>
     <row r="214" spans="1:8" ht="42" customHeight="1">
       <c r="A214" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>20</v>
@@ -7367,10 +7385,10 @@
         <v>23</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>20</v>
@@ -7378,13 +7396,13 @@
     </row>
     <row r="215" spans="1:8" ht="42" customHeight="1">
       <c r="A215" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>20</v>
@@ -7393,10 +7411,10 @@
         <v>23</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H215" s="1" t="s">
         <v>20</v>
@@ -7404,13 +7422,13 @@
     </row>
     <row r="216" spans="1:8" ht="42" customHeight="1">
       <c r="A216" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>20</v>
@@ -7419,10 +7437,10 @@
         <v>23</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>59</v>
+        <v>209</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H216" s="1" t="s">
         <v>20</v>
@@ -7430,10 +7448,10 @@
     </row>
     <row r="217" spans="1:8" ht="42" customHeight="1">
       <c r="A217" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>22</v>
@@ -7445,10 +7463,10 @@
         <v>23</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>20</v>
@@ -7456,25 +7474,25 @@
     </row>
     <row r="218" spans="1:8" ht="42" customHeight="1">
       <c r="A218" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E218" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H218" s="1" t="s">
         <v>20</v>
@@ -7482,16 +7500,16 @@
     </row>
     <row r="219" spans="1:8" ht="42" customHeight="1">
       <c r="A219" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>17</v>
@@ -7500,7 +7518,7 @@
         <v>215</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H219" s="1" t="s">
         <v>20</v>
@@ -7508,25 +7526,25 @@
     </row>
     <row r="220" spans="1:8" ht="42" customHeight="1">
       <c r="A220" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>20</v>
@@ -7534,25 +7552,25 @@
     </row>
     <row r="221" spans="1:8" ht="54" customHeight="1">
       <c r="A221" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E221" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="G221" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>20</v>
@@ -7560,7 +7578,7 @@
     </row>
     <row r="222" spans="1:8" ht="42" customHeight="1">
       <c r="A222" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>220</v>
@@ -7572,13 +7590,13 @@
         <v>20</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>221</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H222" s="1" t="s">
         <v>20</v>
@@ -7586,25 +7604,25 @@
     </row>
     <row r="223" spans="1:8" ht="42" customHeight="1">
       <c r="A223" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>222</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>223</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>20</v>
@@ -7612,77 +7630,77 @@
     </row>
     <row r="224" spans="1:8" ht="42" customHeight="1">
       <c r="A224" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="42" customHeight="1">
       <c r="A225" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>227</v>
+        <v>14</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="42" customHeight="1">
       <c r="A226" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>20</v>
@@ -7690,10 +7708,10 @@
     </row>
     <row r="227" spans="1:8" ht="42" customHeight="1">
       <c r="A227" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>22</v>
@@ -7705,10 +7723,10 @@
         <v>23</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>20</v>
@@ -7716,10 +7734,10 @@
     </row>
     <row r="228" spans="1:8" ht="42" customHeight="1">
       <c r="A228" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>22</v>
@@ -7731,10 +7749,10 @@
         <v>23</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>20</v>
@@ -7742,25 +7760,25 @@
     </row>
     <row r="229" spans="1:8" ht="42" customHeight="1">
       <c r="A229" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>20</v>
@@ -7768,25 +7786,25 @@
     </row>
     <row r="230" spans="1:8" ht="42" customHeight="1">
       <c r="A230" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H230" s="1" t="s">
         <v>20</v>
@@ -7794,16 +7812,16 @@
     </row>
     <row r="231" spans="1:8" ht="42" customHeight="1">
       <c r="A231" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>17</v>
@@ -7812,7 +7830,7 @@
         <v>239</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>20</v>
@@ -7820,7 +7838,7 @@
     </row>
     <row r="232" spans="1:8" ht="42" customHeight="1">
       <c r="A232" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>240</v>
@@ -7838,7 +7856,7 @@
         <v>241</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H232" s="1" t="s">
         <v>20</v>
@@ -7846,13 +7864,13 @@
     </row>
     <row r="233" spans="1:8" ht="42" customHeight="1">
       <c r="A233" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>20</v>
@@ -7864,7 +7882,7 @@
         <v>243</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H233" s="1" t="s">
         <v>20</v>
@@ -7872,13 +7890,13 @@
     </row>
     <row r="234" spans="1:8" ht="42" customHeight="1">
       <c r="A234" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>20</v>
@@ -7890,7 +7908,7 @@
         <v>245</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>20</v>
@@ -7898,7 +7916,7 @@
     </row>
     <row r="235" spans="1:8" ht="42" customHeight="1">
       <c r="A235" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>246</v>
@@ -7916,7 +7934,7 @@
         <v>247</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>20</v>
@@ -7924,36 +7942,36 @@
     </row>
     <row r="236" spans="1:8" ht="42" customHeight="1">
       <c r="A236" s="1" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="42" customHeight="1">
       <c r="A237" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>251</v>
+        <v>72</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>15</v>
@@ -7965,36 +7983,36 @@
         <v>17</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="42" customHeight="1">
       <c r="A238" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>20</v>
@@ -8002,10 +8020,10 @@
     </row>
     <row r="239" spans="1:8" ht="42" customHeight="1">
       <c r="A239" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>22</v>
@@ -8017,10 +8035,10 @@
         <v>23</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H239" s="1" t="s">
         <v>20</v>
@@ -8028,39 +8046,39 @@
     </row>
     <row r="240" spans="1:8" ht="42" customHeight="1">
       <c r="A240" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="42" customHeight="1">
       <c r="A241" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>257</v>
@@ -8069,36 +8087,36 @@
         <v>17</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="42" customHeight="1">
       <c r="A242" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>20</v>
@@ -8106,10 +8124,10 @@
     </row>
     <row r="243" spans="1:8" ht="42" customHeight="1">
       <c r="A243" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>22</v>
@@ -8121,10 +8139,10 @@
         <v>23</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>20</v>
@@ -8132,13 +8150,13 @@
     </row>
     <row r="244" spans="1:8" ht="42" customHeight="1">
       <c r="A244" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>20</v>
@@ -8147,10 +8165,10 @@
         <v>23</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H244" s="1" t="s">
         <v>20</v>
@@ -8158,13 +8176,13 @@
     </row>
     <row r="245" spans="1:8" ht="42" customHeight="1">
       <c r="A245" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>20</v>
@@ -8173,10 +8191,10 @@
         <v>23</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H245" s="1" t="s">
         <v>20</v>
@@ -8184,13 +8202,13 @@
     </row>
     <row r="246" spans="1:8" ht="42" customHeight="1">
       <c r="A246" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>20</v>
@@ -8199,10 +8217,10 @@
         <v>23</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>20</v>
@@ -8210,39 +8228,39 @@
     </row>
     <row r="247" spans="1:8" ht="42" customHeight="1">
       <c r="A247" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>130</v>
+        <v>261</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="42" customHeight="1">
       <c r="A248" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>262</v>
@@ -8251,36 +8269,36 @@
         <v>17</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="42" customHeight="1">
       <c r="A249" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H249" s="1" t="s">
         <v>20</v>
@@ -8288,25 +8306,25 @@
     </row>
     <row r="250" spans="1:8" ht="42" customHeight="1">
       <c r="A250" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>266</v>
+        <v>56</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>20</v>
@@ -8314,13 +8332,13 @@
     </row>
     <row r="251" spans="1:8" ht="42" customHeight="1">
       <c r="A251" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>20</v>
@@ -8329,10 +8347,10 @@
         <v>23</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>20</v>
@@ -8340,25 +8358,25 @@
     </row>
     <row r="252" spans="1:8" ht="42" customHeight="1">
       <c r="A252" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>57</v>
+        <v>265</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>59</v>
+        <v>267</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H252" s="1" t="s">
         <v>20</v>
@@ -8366,36 +8384,36 @@
     </row>
     <row r="253" spans="1:8" ht="42" customHeight="1">
       <c r="A253" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="42" customHeight="1">
       <c r="A254" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>15</v>
@@ -8407,36 +8425,36 @@
         <v>17</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>273</v>
+        <v>108</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="255" spans="1:8" ht="42" customHeight="1">
       <c r="A255" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>20</v>
@@ -8444,10 +8462,10 @@
     </row>
     <row r="256" spans="1:8" ht="42" customHeight="1">
       <c r="A256" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>22</v>
@@ -8459,10 +8477,10 @@
         <v>23</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H256" s="1" t="s">
         <v>20</v>
@@ -8470,25 +8488,25 @@
     </row>
     <row r="257" spans="1:8" ht="42" customHeight="1">
       <c r="A257" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>25</v>
+        <v>274</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>26</v>
+        <v>276</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H257" s="1" t="s">
         <v>20</v>
@@ -8496,13 +8514,13 @@
     </row>
     <row r="258" spans="1:8" ht="42" customHeight="1">
       <c r="A258" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>277</v>
@@ -8511,10 +8529,10 @@
         <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H258" s="1" t="s">
         <v>20</v>
@@ -8522,25 +8540,25 @@
     </row>
     <row r="259" spans="1:8" ht="42" customHeight="1">
       <c r="A259" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>279</v>
+        <v>20</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>186</v>
+        <v>279</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H259" s="1" t="s">
         <v>20</v>
@@ -8548,7 +8566,7 @@
     </row>
     <row r="260" spans="1:8" ht="42" customHeight="1">
       <c r="A260" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>280</v>
@@ -8566,7 +8584,7 @@
         <v>281</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H260" s="1" t="s">
         <v>20</v>
@@ -8574,65 +8592,65 @@
     </row>
     <row r="261" spans="1:8" ht="42" customHeight="1">
       <c r="A261" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="42" customHeight="1">
       <c r="A262" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>285</v>
+        <v>100</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>286</v>
+        <v>102</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263" spans="1:8" ht="42" customHeight="1">
       <c r="A263" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>287</v>
@@ -8641,10 +8659,10 @@
         <v>17</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H263" s="1" t="s">
         <v>20</v>
@@ -8652,10 +8670,10 @@
     </row>
     <row r="264" spans="1:8" ht="42" customHeight="1">
       <c r="A264" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>15</v>
@@ -8667,10 +8685,10 @@
         <v>17</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H264" s="1" t="s">
         <v>20</v>
@@ -8678,10 +8696,10 @@
     </row>
     <row r="265" spans="1:8" ht="42" customHeight="1">
       <c r="A265" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>15</v>
@@ -8693,10 +8711,10 @@
         <v>17</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H265" s="1" t="s">
         <v>20</v>
@@ -8704,10 +8722,10 @@
     </row>
     <row r="266" spans="1:8" ht="42" customHeight="1">
       <c r="A266" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>15</v>
@@ -8719,10 +8737,10 @@
         <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H266" s="1" t="s">
         <v>20</v>
@@ -8730,25 +8748,25 @@
     </row>
     <row r="267" spans="1:8" ht="42" customHeight="1">
       <c r="A267" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>258</v>
+        <v>115</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H267" s="1" t="s">
         <v>20</v>
@@ -8756,10 +8774,10 @@
     </row>
     <row r="268" spans="1:8" ht="42" customHeight="1">
       <c r="A268" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>15</v>
@@ -8771,10 +8789,10 @@
         <v>23</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H268" s="1" t="s">
         <v>20</v>
@@ -8782,65 +8800,65 @@
     </row>
     <row r="269" spans="1:8" ht="42" customHeight="1">
       <c r="A269" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>116</v>
+        <v>292</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>117</v>
+        <v>294</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="270" spans="1:8" ht="42" customHeight="1">
       <c r="A270" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>293</v>
+        <v>30</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>165</v>
+        <v>295</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:8" ht="42" customHeight="1">
       <c r="A271" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>30</v>
+        <v>259</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>287</v>
@@ -8849,10 +8867,10 @@
         <v>17</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>32</v>
+        <v>261</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>20</v>
@@ -8860,10 +8878,10 @@
     </row>
     <row r="272" spans="1:8" ht="42" customHeight="1">
       <c r="A272" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>15</v>
@@ -8875,10 +8893,10 @@
         <v>17</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>20</v>
@@ -8886,25 +8904,25 @@
     </row>
     <row r="273" spans="1:8" ht="42" customHeight="1">
       <c r="A273" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H273" s="1" t="s">
         <v>20</v>
@@ -8912,25 +8930,25 @@
     </row>
     <row r="274" spans="1:8" ht="42" customHeight="1">
       <c r="A274" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>229</v>
+        <v>41</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>20</v>
@@ -8938,10 +8956,10 @@
     </row>
     <row r="275" spans="1:8" ht="42" customHeight="1">
       <c r="A275" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>22</v>
@@ -8953,10 +8971,10 @@
         <v>23</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H275" s="1" t="s">
         <v>20</v>
@@ -8964,13 +8982,13 @@
     </row>
     <row r="276" spans="1:8" ht="42" customHeight="1">
       <c r="A276" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>20</v>
@@ -8979,10 +8997,10 @@
         <v>23</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>20</v>
@@ -8990,10 +9008,10 @@
     </row>
     <row r="277" spans="1:8" ht="42" customHeight="1">
       <c r="A277" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>45</v>
@@ -9005,10 +9023,10 @@
         <v>23</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H277" s="1" t="s">
         <v>20</v>
@@ -9016,77 +9034,77 @@
     </row>
     <row r="278" spans="1:8" ht="42" customHeight="1">
       <c r="A278" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>47</v>
+        <v>298</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="279" spans="1:8" ht="42" customHeight="1">
       <c r="A279" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>165</v>
+        <v>301</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="42" customHeight="1">
       <c r="A280" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H280" s="1" t="s">
         <v>20</v>
@@ -9094,25 +9112,25 @@
     </row>
     <row r="281" spans="1:8" ht="42" customHeight="1">
       <c r="A281" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H281" s="1" t="s">
         <v>20</v>
@@ -9120,25 +9138,25 @@
     </row>
     <row r="282" spans="1:8" ht="42" customHeight="1">
       <c r="A282" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H282" s="1" t="s">
         <v>20</v>
@@ -9146,25 +9164,25 @@
     </row>
     <row r="283" spans="1:8" ht="42" customHeight="1">
       <c r="A283" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>20</v>
@@ -9172,25 +9190,25 @@
     </row>
     <row r="284" spans="1:8" ht="42" customHeight="1">
       <c r="A284" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>301</v>
+        <v>249</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H284" s="1" t="s">
         <v>20</v>
@@ -9198,25 +9216,25 @@
     </row>
     <row r="285" spans="1:8" ht="42" customHeight="1">
       <c r="A285" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H285" s="1" t="s">
         <v>20</v>
@@ -9224,25 +9242,25 @@
     </row>
     <row r="286" spans="1:8" ht="42" customHeight="1">
       <c r="A286" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H286" s="1" t="s">
         <v>20</v>
@@ -9250,13 +9268,13 @@
     </row>
     <row r="287" spans="1:8" ht="42" customHeight="1">
       <c r="A287" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>192</v>
+        <v>45</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>20</v>
@@ -9265,10 +9283,10 @@
         <v>17</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H287" s="1" t="s">
         <v>20</v>
@@ -9276,25 +9294,25 @@
     </row>
     <row r="288" spans="1:8" ht="42" customHeight="1">
       <c r="A288" s="1" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>230</v>
+        <v>317</v>
       </c>
       <c r="H288" s="1" t="s">
         <v>20</v>
@@ -9302,25 +9320,25 @@
     </row>
     <row r="289" spans="1:8" ht="42" customHeight="1">
       <c r="A289" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="H289" s="1" t="s">
         <v>20</v>
@@ -9328,10 +9346,10 @@
     </row>
     <row r="290" spans="1:8" ht="42" customHeight="1">
       <c r="A290" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>22</v>
@@ -9343,10 +9361,10 @@
         <v>17</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="H290" s="1" t="s">
         <v>20</v>
@@ -9354,10 +9372,10 @@
     </row>
     <row r="291" spans="1:8" ht="42" customHeight="1">
       <c r="A291" s="1" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>315</v>
+        <v>203</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>22</v>
@@ -9366,13 +9384,13 @@
         <v>20</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>316</v>
+        <v>205</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>312</v>
+        <v>228</v>
       </c>
       <c r="H291" s="1" t="s">
         <v>20</v>
@@ -9380,10 +9398,10 @@
     </row>
     <row r="292" spans="1:8" ht="42" customHeight="1">
       <c r="A292" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>22</v>
@@ -9392,13 +9410,13 @@
         <v>20</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H292" s="1" t="s">
         <v>20</v>
@@ -9406,10 +9424,10 @@
     </row>
     <row r="293" spans="1:8" ht="42" customHeight="1">
       <c r="A293" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>265</v>
+        <v>323</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>22</v>
@@ -9418,13 +9436,13 @@
         <v>20</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>20</v>
@@ -9432,25 +9450,25 @@
     </row>
     <row r="294" spans="1:8" ht="42" customHeight="1">
       <c r="A294" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H294" s="1" t="s">
         <v>20</v>
@@ -9458,25 +9476,25 @@
     </row>
     <row r="295" spans="1:8" ht="54" customHeight="1">
       <c r="A295" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H295" s="1" t="s">
         <v>20</v>
@@ -9484,25 +9502,25 @@
     </row>
     <row r="296" spans="1:8" ht="42" customHeight="1">
       <c r="A296" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H296" s="1" t="s">
         <v>20</v>
@@ -9510,25 +9528,25 @@
     </row>
     <row r="297" spans="1:8" ht="42" customHeight="1">
       <c r="A297" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H297" s="1" t="s">
         <v>20</v>
@@ -9536,25 +9554,25 @@
     </row>
     <row r="298" spans="1:8" ht="54" customHeight="1">
       <c r="A298" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H298" s="1" t="s">
         <v>20</v>
@@ -9562,25 +9580,25 @@
     </row>
     <row r="299" spans="1:8" ht="42" customHeight="1">
       <c r="A299" s="1" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>329</v>
+        <v>203</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>330</v>
+        <v>205</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="H299" s="1" t="s">
         <v>20</v>
@@ -9588,10 +9606,10 @@
     </row>
     <row r="300" spans="1:8" ht="42" customHeight="1">
       <c r="A300" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>22</v>
@@ -9600,13 +9618,13 @@
         <v>20</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H300" s="1" t="s">
         <v>20</v>
@@ -9614,10 +9632,10 @@
     </row>
     <row r="301" spans="1:8" ht="42" customHeight="1">
       <c r="A301" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>265</v>
+        <v>129</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>22</v>
@@ -9626,13 +9644,13 @@
         <v>20</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>266</v>
+        <v>130</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H301" s="1" t="s">
         <v>20</v>
@@ -9640,25 +9658,25 @@
     </row>
     <row r="302" spans="1:8" ht="42" customHeight="1">
       <c r="A302" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>129</v>
+        <v>336</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H302" s="1" t="s">
         <v>20</v>
@@ -9666,25 +9684,25 @@
     </row>
     <row r="303" spans="1:8" ht="42" customHeight="1">
       <c r="A303" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H303" s="1" t="s">
         <v>20</v>
@@ -9692,10 +9710,10 @@
     </row>
     <row r="304" spans="1:8" ht="42" customHeight="1">
       <c r="A304" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>15</v>
@@ -9704,13 +9722,13 @@
         <v>20</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H304" s="1" t="s">
         <v>20</v>
@@ -9718,25 +9736,25 @@
     </row>
     <row r="305" spans="1:8" ht="42" customHeight="1">
       <c r="A305" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H305" s="1" t="s">
         <v>20</v>
@@ -9744,25 +9762,25 @@
     </row>
     <row r="306" spans="1:8" ht="42" customHeight="1">
       <c r="A306" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H306" s="1" t="s">
         <v>20</v>
@@ -9770,25 +9788,25 @@
     </row>
     <row r="307" spans="1:8" ht="54" customHeight="1">
       <c r="A307" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H307" s="1" t="s">
         <v>20</v>
@@ -9796,10 +9814,10 @@
     </row>
     <row r="308" spans="1:8" ht="42" customHeight="1">
       <c r="A308" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>38</v>
@@ -9808,13 +9826,13 @@
         <v>20</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H308" s="1" t="s">
         <v>20</v>
@@ -9822,10 +9840,10 @@
     </row>
     <row r="309" spans="1:8" ht="42" customHeight="1">
       <c r="A309" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>38</v>
@@ -9834,13 +9852,13 @@
         <v>20</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H309" s="1" t="s">
         <v>20</v>
@@ -9848,25 +9866,25 @@
     </row>
     <row r="310" spans="1:8" ht="42" customHeight="1">
       <c r="A310" s="1" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>329</v>
+        <v>203</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>330</v>
+        <v>205</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="H310" s="1" t="s">
         <v>20</v>
@@ -9874,10 +9892,10 @@
     </row>
     <row r="311" spans="1:8" ht="42" customHeight="1">
       <c r="A311" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>22</v>
@@ -9886,13 +9904,13 @@
         <v>20</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H311" s="1" t="s">
         <v>20</v>
@@ -9900,25 +9918,25 @@
     </row>
     <row r="312" spans="1:8" ht="42" customHeight="1">
       <c r="A312" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H312" s="1" t="s">
         <v>20</v>
@@ -9926,25 +9944,25 @@
     </row>
     <row r="313" spans="1:8" ht="42" customHeight="1">
       <c r="A313" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H313" s="1" t="s">
         <v>20</v>
@@ -9952,25 +9970,25 @@
     </row>
     <row r="314" spans="1:8" ht="42" customHeight="1">
       <c r="A314" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H314" s="1" t="s">
         <v>20</v>
@@ -9978,25 +9996,25 @@
     </row>
     <row r="315" spans="1:8" ht="42" customHeight="1">
       <c r="A315" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H315" s="1" t="s">
         <v>20</v>
@@ -10004,25 +10022,25 @@
     </row>
     <row r="316" spans="1:8" ht="54" customHeight="1">
       <c r="A316" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>20</v>
@@ -10030,10 +10048,10 @@
     </row>
     <row r="317" spans="1:8" ht="42" customHeight="1">
       <c r="A317" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>127</v>
@@ -10042,13 +10060,13 @@
         <v>20</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H317" s="1" t="s">
         <v>20</v>
@@ -10056,25 +10074,25 @@
     </row>
     <row r="318" spans="1:8" ht="42" customHeight="1">
       <c r="A318" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H318" s="1" t="s">
         <v>20</v>
@@ -10082,25 +10100,25 @@
     </row>
     <row r="319" spans="1:8" ht="42" customHeight="1">
       <c r="A319" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H319" s="1" t="s">
         <v>20</v>
@@ -10108,25 +10126,25 @@
     </row>
     <row r="320" spans="1:8" ht="42" customHeight="1">
       <c r="A320" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H320" s="1" t="s">
         <v>20</v>
@@ -10134,25 +10152,25 @@
     </row>
     <row r="321" spans="1:8" ht="42" customHeight="1">
       <c r="A321" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H321" s="1" t="s">
         <v>20</v>
@@ -10160,25 +10178,25 @@
     </row>
     <row r="322" spans="1:8" ht="42" customHeight="1">
       <c r="A322" s="1" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>329</v>
+        <v>203</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>330</v>
+        <v>205</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="H322" s="1" t="s">
         <v>20</v>
@@ -10186,10 +10204,10 @@
     </row>
     <row r="323" spans="1:8" ht="42" customHeight="1">
       <c r="A323" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>22</v>
@@ -10198,13 +10216,13 @@
         <v>20</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>20</v>
@@ -10212,10 +10230,10 @@
     </row>
     <row r="324" spans="1:8" ht="42" customHeight="1">
       <c r="A324" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>22</v>
@@ -10224,13 +10242,13 @@
         <v>20</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>266</v>
+        <v>370</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H324" s="1" t="s">
         <v>20</v>
@@ -10238,10 +10256,10 @@
     </row>
     <row r="325" spans="1:8" ht="42" customHeight="1">
       <c r="A325" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>365</v>
+        <v>176</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>22</v>
@@ -10250,13 +10268,13 @@
         <v>20</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>366</v>
+        <v>177</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H325" s="1" t="s">
         <v>20</v>
@@ -10264,25 +10282,25 @@
     </row>
     <row r="326" spans="1:8" ht="42" customHeight="1">
       <c r="A326" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>177</v>
+        <v>371</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>178</v>
+        <v>372</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H326" s="1" t="s">
         <v>20</v>
@@ -10290,25 +10308,25 @@
     </row>
     <row r="327" spans="1:8" ht="42" customHeight="1">
       <c r="A327" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="H327" s="1" t="s">
         <v>20</v>
@@ -10316,22 +10334,22 @@
     </row>
     <row r="328" spans="1:8" ht="42" customHeight="1">
       <c r="A328" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>370</v>
+        <v>211</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>371</v>
+        <v>213</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>19</v>
@@ -10342,16 +10360,16 @@
     </row>
     <row r="329" spans="1:8" ht="42" customHeight="1">
       <c r="A329" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>17</v>
@@ -10368,65 +10386,65 @@
     </row>
     <row r="330" spans="1:8" ht="42" customHeight="1">
       <c r="A330" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>214</v>
+        <v>378</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>217</v>
+        <v>379</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
     <row r="331" spans="1:8" ht="42" customHeight="1">
       <c r="A331" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
     </row>
     <row r="332" spans="1:8" ht="42" customHeight="1">
       <c r="A332" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>20</v>
@@ -10435,21 +10453,21 @@
         <v>17</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>20</v>
+        <v>384</v>
       </c>
     </row>
     <row r="333" spans="1:8" ht="42" customHeight="1">
       <c r="A333" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>87</v>
@@ -10458,50 +10476,50 @@
         <v>20</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>380</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334" spans="1:8" ht="42" customHeight="1">
       <c r="A334" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="335" spans="1:8" ht="42" customHeight="1">
       <c r="A335" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>149</v>
@@ -10513,21 +10531,21 @@
         <v>17</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="336" spans="1:8" ht="42" customHeight="1">
       <c r="A336" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>149</v>
@@ -10539,24 +10557,24 @@
         <v>17</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="337" spans="1:8" ht="42" customHeight="1">
       <c r="A337" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>388</v>
+        <v>182</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>20</v>
@@ -10565,21 +10583,21 @@
         <v>17</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="338" spans="1:8" ht="54" customHeight="1">
       <c r="A338" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>183</v>
+        <v>396</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>22</v>
@@ -10588,39 +10606,39 @@
         <v>20</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>391</v>
+        <v>20</v>
       </c>
     </row>
     <row r="339" spans="1:8" ht="42" customHeight="1">
       <c r="A339" s="1" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="H339" s="1" t="s">
         <v>20</v>
@@ -10628,10 +10646,10 @@
     </row>
     <row r="340" spans="1:8" ht="42" customHeight="1">
       <c r="A340" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>395</v>
+        <v>320</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>22</v>
@@ -10640,13 +10658,13 @@
         <v>20</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>396</v>
+        <v>321</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H340" s="1" t="s">
         <v>20</v>
@@ -10654,10 +10672,10 @@
     </row>
     <row r="341" spans="1:8" ht="42" customHeight="1">
       <c r="A341" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>22</v>
@@ -10666,13 +10684,13 @@
         <v>20</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H341" s="1" t="s">
         <v>20</v>
@@ -10680,10 +10698,10 @@
     </row>
     <row r="342" spans="1:8" ht="42" customHeight="1">
       <c r="A342" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>22</v>
@@ -10692,13 +10710,13 @@
         <v>20</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>20</v>
@@ -10706,58 +10724,32 @@
     </row>
     <row r="343" spans="1:8" ht="42" customHeight="1">
       <c r="A343" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" ht="42" customHeight="1">
-      <c r="A344" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E344" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F344" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="G344" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="H344" s="1" t="s">
-        <v>20</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H344" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:H343" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
@@ -10786,7 +10778,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="26.1" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -10800,7 +10792,7 @@
     </row>
     <row r="2" spans="1:4" ht="26.1" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -10814,7 +10806,7 @@
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
@@ -10828,7 +10820,7 @@
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>1</v>
@@ -10845,13 +10837,13 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42" customHeight="1">
@@ -10859,7 +10851,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -10873,7 +10865,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
@@ -10887,7 +10879,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
@@ -10901,7 +10893,7 @@
         <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
@@ -10915,7 +10907,7 @@
         <v>71</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
@@ -10929,7 +10921,7 @@
         <v>79</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>83</v>
@@ -10943,7 +10935,7 @@
         <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>83</v>
@@ -10957,7 +10949,7 @@
         <v>99</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -10971,7 +10963,7 @@
         <v>118</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>19</v>
@@ -10985,7 +10977,7 @@
         <v>131</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>19</v>
@@ -10999,7 +10991,7 @@
         <v>135</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>19</v>
@@ -11013,7 +11005,7 @@
         <v>143</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>19</v>
@@ -11024,10 +11016,10 @@
     </row>
     <row r="18" spans="1:4" ht="42" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>19</v>
@@ -11038,10 +11030,10 @@
     </row>
     <row r="19" spans="1:4" ht="42" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>19</v>
@@ -11052,10 +11044,10 @@
     </row>
     <row r="20" spans="1:4" ht="42" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>19</v>
@@ -11066,10 +11058,10 @@
     </row>
     <row r="21" spans="1:4" ht="42" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>19</v>
@@ -11080,10 +11072,10 @@
     </row>
     <row r="22" spans="1:4" ht="42" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>19</v>
@@ -11094,10 +11086,10 @@
     </row>
     <row r="23" spans="1:4" ht="42" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>19</v>
@@ -11108,10 +11100,10 @@
     </row>
     <row r="24" spans="1:4" ht="42" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>19</v>
@@ -11122,10 +11114,10 @@
     </row>
     <row r="25" spans="1:4" ht="42" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>19</v>
@@ -11136,10 +11128,10 @@
     </row>
     <row r="26" spans="1:4" ht="42" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>19</v>
@@ -11150,10 +11142,10 @@
     </row>
     <row r="27" spans="1:4" ht="42" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>19</v>
@@ -11164,13 +11156,13 @@
     </row>
     <row r="28" spans="1:4" ht="42" customHeight="1">
       <c r="A28" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="D28" s="1">
         <v>7</v>
@@ -11178,13 +11170,13 @@
     </row>
     <row r="29" spans="1:4" ht="42" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D29" s="1">
         <v>5</v>
@@ -11192,13 +11184,13 @@
     </row>
     <row r="30" spans="1:4" ht="42" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D30" s="1">
         <v>8</v>
@@ -11206,13 +11198,13 @@
     </row>
     <row r="31" spans="1:4" ht="54" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D31" s="1">
         <v>14</v>
@@ -11220,27 +11212,27 @@
     </row>
     <row r="32" spans="1:4" ht="42" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D32" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="54" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D33" s="1">
         <v>8</v>
@@ -11248,13 +11240,13 @@
     </row>
     <row r="34" spans="1:4" ht="42" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D34" s="1">
         <v>6</v>
@@ -11262,13 +11254,13 @@
     </row>
     <row r="35" spans="1:4" ht="42" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D35" s="1">
         <v>5</v>
@@ -11276,13 +11268,13 @@
     </row>
     <row r="36" spans="1:4" ht="42" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D36" s="1">
         <v>7</v>
@@ -11290,13 +11282,13 @@
     </row>
     <row r="37" spans="1:4" ht="42" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D37" s="1">
         <v>4</v>
@@ -11304,13 +11296,13 @@
     </row>
     <row r="38" spans="1:4" ht="42" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D38" s="1">
         <v>7</v>
@@ -11318,13 +11310,13 @@
     </row>
     <row r="39" spans="1:4" ht="42" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D39" s="1">
         <v>6</v>
@@ -11332,13 +11324,13 @@
     </row>
     <row r="40" spans="1:4" ht="42" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D40" s="1">
         <v>4</v>
@@ -11346,13 +11338,13 @@
     </row>
     <row r="41" spans="1:4" ht="42" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D41" s="1">
         <v>4</v>
@@ -11360,13 +11352,13 @@
     </row>
     <row r="42" spans="1:4" ht="42" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D42" s="1">
         <v>8</v>
@@ -11374,13 +11366,13 @@
     </row>
     <row r="43" spans="1:4" ht="42" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D43" s="1">
         <v>9</v>
@@ -11388,13 +11380,13 @@
     </row>
     <row r="44" spans="1:4" ht="42" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D44" s="1">
         <v>10</v>
@@ -11402,13 +11394,13 @@
     </row>
     <row r="45" spans="1:4" ht="42" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -11416,13 +11408,13 @@
     </row>
     <row r="46" spans="1:4" ht="54" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D46" s="1">
         <v>8</v>
@@ -11430,13 +11422,13 @@
     </row>
     <row r="47" spans="1:4" ht="42" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D47" s="1">
         <v>11</v>
@@ -11444,13 +11436,13 @@
     </row>
     <row r="48" spans="1:4" ht="72" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D48" s="1">
         <v>12</v>
@@ -11458,13 +11450,13 @@
     </row>
     <row r="49" spans="1:4" ht="72" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D49" s="1">
         <v>5</v>
@@ -11472,10 +11464,10 @@
     </row>
     <row r="50" spans="1:4" ht="54" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>19</v>
@@ -11486,10 +11478,10 @@
     </row>
     <row r="51" spans="1:4" ht="42" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>83</v>
@@ -11500,13 +11492,13 @@
     </row>
     <row r="52" spans="1:4" ht="42" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D52" s="1">
         <v>5</v>
@@ -11527,17 +11519,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f980afce-1032-46c3-98e6-ac5716cd24fb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7c6b5d28-3521-41f5-b993-40f3bc87f56c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E612D71E453074BAD0BA4FF167E6B43" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7dc4f0e003beb21372302810037fa9a7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f980afce-1032-46c3-98e6-ac5716cd24fb" xmlns:ns3="7c6b5d28-3521-41f5-b993-40f3bc87f56c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3a3c444de25cad6eaed294ff13f6a3ef" ns2:_="" ns3:_="">
     <xsd:import namespace="f980afce-1032-46c3-98e6-ac5716cd24fb"/>
@@ -11724,7 +11705,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11733,14 +11714,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f980afce-1032-46c3-98e6-ac5716cd24fb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7c6b5d28-3521-41f5-b993-40f3bc87f56c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E1FC448-101D-4FC2-93BB-E15D1177325B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D05076F6-214D-4B80-B09A-64B8E81C5264}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A90BB198-D8AE-4072-A332-767AE17F5016}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B9B6373-28DA-4BBB-8DC8-5C8A0350D11B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED7FF02-5340-49C2-A743-E7691129EAD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C5A96B-4705-4C84-8F60-BBC1AF3311A0}"/>
 </file>